--- a/src/test/resources/TestDriver/Hearst_ESQ/ActivityData/ESQ_AP.xlsx
+++ b/src/test/resources/TestDriver/Hearst_ESQ/ActivityData/ESQ_AP.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D117"/>
+  <dimension ref="A1:F117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -438,6 +438,16 @@
           <t>standalone_price_policy</t>
         </is>
       </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>parent_child</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>parent_code</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -458,6 +468,11 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Parent</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -478,6 +493,11 @@
           <t>SALE_PRICE</t>
         </is>
       </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Parent</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -498,6 +518,11 @@
           <t>SALE_PRICE</t>
         </is>
       </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Parent</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -518,6 +543,11 @@
           <t>SALE_PRICE</t>
         </is>
       </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Parent</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -538,6 +568,11 @@
           <t>SALE_PRICE</t>
         </is>
       </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Parent</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -558,6 +593,11 @@
           <t>SALE_PRICE</t>
         </is>
       </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Parent</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -578,6 +618,11 @@
           <t>SALE_PRICE</t>
         </is>
       </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Parent</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -598,6 +643,11 @@
           <t>SALE_PRICE</t>
         </is>
       </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Parent</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -618,6 +668,11 @@
           <t>SALE_PRICE</t>
         </is>
       </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Parent</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -638,6 +693,11 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Parent</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -658,6 +718,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>ESQ_PREM_PRTDIG_CAN_New_60</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -678,6 +748,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>ESQ_PREM_PRTDIG_CAN_New_60</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -698,6 +778,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>ESQ_PREM_PRTDIG_CAN_New_60</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -718,6 +808,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>ESQ_PREM_PRTDIG_CAN_New_60</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -738,6 +838,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>ESQ_PREM_PRTDIG_CAN_New_60</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -758,6 +868,11 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Parent</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -778,6 +893,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>ESQ_PREM_PRTDIG_GIFT_US_50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -798,6 +923,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>ESQ_PREM_PRTDIG_GIFT_US_50</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -818,6 +953,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>ESQ_PREM_PRTDIG_GIFT_US_50</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -838,6 +983,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>ESQ_PREM_PRTDIG_GIFT_US_50</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -858,6 +1013,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>ESQ_PREM_PRTDIG_GIFT_US_50</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -878,6 +1043,11 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Parent</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -898,6 +1068,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>ESQ_PREM_PRTDIG_MGRT_US_Renew_75</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -918,6 +1098,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>ESQ_PREM_PRTDIG_MGRT_US_Renew_75</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -938,6 +1128,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>ESQ_PREM_PRTDIG_MGRT_US_Renew_75</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -958,6 +1158,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>ESQ_PREM_PRTDIG_MGRT_US_Renew_75</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -978,6 +1188,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>ESQ_PREM_PRTDIG_MGRT_US_Renew_75</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -998,6 +1218,11 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Parent</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1018,6 +1243,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>ESQ_PREM_PRTDIG_UPGRADE_US_50</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1038,6 +1273,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>ESQ_PREM_PRTDIG_UPGRADE_US_50</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1058,6 +1303,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>ESQ_PREM_PRTDIG_UPGRADE_US_50</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1078,6 +1333,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>ESQ_PREM_PRTDIG_UPGRADE_US_50</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1098,6 +1363,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>ESQ_PREM_PRTDIG_UPGRADE_US_50</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1118,6 +1393,11 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Parent</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1138,6 +1418,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>ESQ_PREM_PRTDIG_US_New_40</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1158,6 +1448,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>ESQ_PREM_PRTDIG_US_New_40</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1178,6 +1478,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>ESQ_PREM_PRTDIG_US_New_40</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1198,6 +1508,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>ESQ_PREM_PRTDIG_US_New_40</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1218,6 +1538,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>ESQ_PREM_PRTDIG_US_New_40</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1238,6 +1568,11 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Parent</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1258,6 +1593,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>ESQ_PREM_PRTDIG_US_New_50</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1278,6 +1623,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>ESQ_PREM_PRTDIG_US_New_50</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1298,6 +1653,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>ESQ_PREM_PRTDIG_US_New_50</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1318,6 +1683,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>ESQ_PREM_PRTDIG_US_New_50</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1338,6 +1713,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>ESQ_PREM_PRTDIG_US_New_50</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1358,6 +1743,11 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Parent</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1378,6 +1768,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>ESQ_PREM_PRTDIG_US_New_65STYLEBK</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1398,6 +1798,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>ESQ_PREM_PRTDIG_US_New_65STYLEBK</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1418,6 +1828,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>ESQ_PREM_PRTDIG_US_New_65STYLEBK</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1438,6 +1858,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>ESQ_PREM_PRTDIG_US_New_65STYLEBK</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1458,6 +1888,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>ESQ_PREM_PRTDIG_US_New_65STYLEBK</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1478,6 +1918,11 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Parent</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1498,6 +1943,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>ESQ_PREM_PRTDIG_US_Renew_75</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1518,6 +1973,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>ESQ_PREM_PRTDIG_US_Renew_75</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1538,6 +2003,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>ESQ_PREM_PRTDIG_US_Renew_75</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1558,6 +2033,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>ESQ_PREM_PRTDIG_US_Renew_75</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1578,6 +2063,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>ESQ_PREM_PRTDIG_US_Renew_75</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1598,6 +2093,11 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Parent</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1618,6 +2118,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>ESQ_PRTDIG_CAN_New_30</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1638,6 +2148,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>ESQ_PRTDIG_CAN_New_30</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -1658,6 +2178,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>ESQ_PRTDIG_CAN_New_30</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -1678,6 +2208,11 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Parent</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -1698,6 +2233,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>ESQ_PRTDIG_CAN_New_34</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -1718,6 +2263,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>ESQ_PRTDIG_CAN_New_34</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -1738,6 +2293,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>ESQ_PRTDIG_CAN_New_34</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -1758,6 +2323,11 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Parent</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -1778,6 +2348,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>ESQ_PRTDIG_CAN_New_40</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -1798,6 +2378,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>ESQ_PRTDIG_CAN_New_40</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -1818,6 +2408,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>ESQ_PRTDIG_CAN_New_40</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -1838,6 +2438,11 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Parent</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -1858,6 +2463,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>ESQ_PRTDIG_CAN_Renew_50</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -1878,6 +2493,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>ESQ_PRTDIG_CAN_Renew_50</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -1898,6 +2523,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>ESQ_PRTDIG_CAN_Renew_50</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -1918,6 +2553,11 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Parent</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -1938,6 +2578,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>ESQ_PRTDIG_GIFT_US_30</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -1958,6 +2608,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>ESQ_PRTDIG_GIFT_US_30</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -1978,6 +2638,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>ESQ_PRTDIG_GIFT_US_30</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -1998,6 +2668,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>ESQ_PRTDIG_GIFT_US_30</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2018,6 +2698,11 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Parent</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -2038,6 +2723,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>ESQ_PRTDIG_MGRT_CAN_Renew_50</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -2058,6 +2753,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>ESQ_PRTDIG_MGRT_CAN_Renew_50</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -2078,6 +2783,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>ESQ_PRTDIG_MGRT_CAN_Renew_50</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -2098,6 +2813,11 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Parent</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -2118,6 +2838,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>ESQ_PRTDIG_MGRT_US_Renew_40</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -2138,6 +2868,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>ESQ_PRTDIG_MGRT_US_Renew_40</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -2158,6 +2898,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>ESQ_PRTDIG_MGRT_US_Renew_40</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -2178,6 +2928,11 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Parent</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -2198,6 +2953,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>ESQ_PRTDIG_US_New_12</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -2218,6 +2983,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>ESQ_PRTDIG_US_New_12</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -2238,6 +3013,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>ESQ_PRTDIG_US_New_12</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -2258,6 +3043,11 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Parent</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -2278,6 +3068,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>ESQ_PRTDIG_US_New_20</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -2298,6 +3098,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>ESQ_PRTDIG_US_New_20</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -2318,6 +3128,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>ESQ_PRTDIG_US_New_20</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -2338,6 +3158,11 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Parent</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -2358,6 +3183,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>ESQ_PRTDIG_US_New_23</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -2378,6 +3213,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>ESQ_PRTDIG_US_New_23</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -2398,6 +3243,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>ESQ_PRTDIG_US_New_23</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -2418,6 +3273,11 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Parent</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -2438,6 +3298,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>ESQ_PRTDIG_US_New_24</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -2458,6 +3328,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>ESQ_PRTDIG_US_New_24</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -2478,6 +3358,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>ESQ_PRTDIG_US_New_24</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -2498,6 +3388,11 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Parent</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -2518,6 +3413,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>ESQ_PRTDIG_US_New_30</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -2538,6 +3443,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>ESQ_PRTDIG_US_New_30</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -2558,6 +3473,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>ESQ_PRTDIG_US_New_30</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -2578,6 +3503,11 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Parent</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -2598,6 +3528,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>ESQ_PRTDIG_US_New_35</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -2618,6 +3558,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>ESQ_PRTDIG_US_New_35</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -2638,6 +3588,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>ESQ_PRTDIG_US_New_35</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -2658,6 +3618,11 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Parent</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -2678,6 +3643,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>ESQ_PRTDIG_US_Renew_40</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -2698,6 +3673,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>ESQ_PRTDIG_US_Renew_40</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -2718,6 +3703,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>ESQ_PRTDIG_US_Renew_40</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -2738,6 +3733,11 @@
           <t>SALE_PRICE</t>
         </is>
       </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Parent</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -2756,6 +3756,11 @@
       <c r="D117" t="inlineStr">
         <is>
           <t>DOLLAR_AMOUNT</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Parent</t>
         </is>
       </c>
     </row>
